--- a/outputs/daily/hr_rankings_2026-08-24.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-24.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -21410,7 +21410,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -34598,7 +34598,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -36796,7 +36796,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -37424,7 +37424,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -40258,7 +40258,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -42234,7 +42234,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
